--- a/seed/out/05_Qoo10_JP_決済明細_2026Q2.xlsx
+++ b/seed/out/05_Qoo10_JP_決済明細_2026Q2.xlsx
@@ -459,49 +459,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026/04/21</t>
+          <t>2026/04/23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1730</v>
+        <v>2011</v>
       </c>
       <c r="E2" t="n">
-        <v>208</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026/04/22</t>
+          <t>2026/04/19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2730</v>
+        <v>3460</v>
       </c>
       <c r="E3" t="n">
-        <v>328</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/04/26</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -522,196 +522,196 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026/04/02</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10876</v>
+        <v>6156</v>
       </c>
       <c r="E5" t="n">
-        <v>1305</v>
+        <v>739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2719</v>
+        <v>1640</v>
       </c>
       <c r="E6" t="n">
-        <v>326</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8496</v>
+        <v>8854</v>
       </c>
       <c r="E7" t="n">
-        <v>1020</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026/04/05</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3078</v>
+        <v>6560</v>
       </c>
       <c r="E8" t="n">
-        <v>369</v>
+        <v>787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026/04/22</t>
+          <t>2026/04/26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>6920</v>
+        <v>10876</v>
       </c>
       <c r="E9" t="n">
-        <v>830</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5460</v>
+        <v>6560</v>
       </c>
       <c r="E10" t="n">
-        <v>655</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/04/07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2124</v>
+        <v>2730</v>
       </c>
       <c r="E11" t="n">
-        <v>255</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026/04/21</t>
+          <t>2026/04/05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1640</v>
+        <v>10876</v>
       </c>
       <c r="E12" t="n">
-        <v>197</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4022</v>
+        <v>6156</v>
       </c>
       <c r="E13" t="n">
-        <v>483</v>
+        <v>739</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/04/14</t>
+          <t>2026/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,55 +720,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4427</v>
+        <v>8854</v>
       </c>
       <c r="E14" t="n">
-        <v>531</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2719</v>
+        <v>4022</v>
       </c>
       <c r="E15" t="n">
-        <v>326</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026/04/19</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1730</v>
+        <v>2124</v>
       </c>
       <c r="E16" t="n">
-        <v>208</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17">
@@ -779,143 +779,143 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>6920</v>
+        <v>6560</v>
       </c>
       <c r="E17" t="n">
-        <v>830</v>
+        <v>787</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026/04/14</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>8854</v>
+        <v>10920</v>
       </c>
       <c r="E18" t="n">
-        <v>1062</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1640</v>
+        <v>2730</v>
       </c>
       <c r="E19" t="n">
-        <v>197</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/04/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1730</v>
+        <v>4427</v>
       </c>
       <c r="E20" t="n">
-        <v>208</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026/04/08</t>
+          <t>2026/04/19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2011</v>
+        <v>1539</v>
       </c>
       <c r="E21" t="n">
-        <v>241</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026/04/18</t>
+          <t>2026/04/16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1539</v>
+        <v>8854</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026/04/06</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10920</v>
+        <v>2124</v>
       </c>
       <c r="E23" t="n">
-        <v>1310</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24">
@@ -926,86 +926,86 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3460</v>
+        <v>3280</v>
       </c>
       <c r="E24" t="n">
-        <v>415</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>6156</v>
+        <v>3460</v>
       </c>
       <c r="E25" t="n">
-        <v>739</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>5438</v>
+        <v>6560</v>
       </c>
       <c r="E26" t="n">
-        <v>653</v>
+        <v>787</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6560</v>
+        <v>2730</v>
       </c>
       <c r="E27" t="n">
-        <v>787</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026/04/06</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2730</v>
+        <v>5460</v>
       </c>
       <c r="E28" t="n">
-        <v>328</v>
+        <v>655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1035,40 +1035,40 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>5460</v>
+        <v>2730</v>
       </c>
       <c r="E29" t="n">
-        <v>655</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>2730</v>
+        <v>4022</v>
       </c>
       <c r="E30" t="n">
-        <v>328</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>4022</v>
+        <v>2011</v>
       </c>
       <c r="E31" t="n">
-        <v>483</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -1144,448 +1144,448 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/05/02</t>
+          <t>2026/05/04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2011</v>
+        <v>3078</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3078</v>
+        <v>3280</v>
       </c>
       <c r="E5" t="n">
-        <v>369</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3280</v>
+        <v>4427</v>
       </c>
       <c r="E6" t="n">
-        <v>394</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4427</v>
+        <v>4022</v>
       </c>
       <c r="E7" t="n">
-        <v>531</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026/05/27</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4022</v>
+        <v>1539</v>
       </c>
       <c r="E8" t="n">
-        <v>483</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1539</v>
+        <v>4427</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4427</v>
+        <v>1539</v>
       </c>
       <c r="E10" t="n">
-        <v>531</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1539</v>
+        <v>8044</v>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026/05/02</t>
+          <t>2026/05/16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8044</v>
+        <v>1640</v>
       </c>
       <c r="E12" t="n">
-        <v>965</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026/05/16</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1640</v>
+        <v>4427</v>
       </c>
       <c r="E13" t="n">
-        <v>197</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4427</v>
+        <v>2011</v>
       </c>
       <c r="E14" t="n">
-        <v>531</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2011</v>
+        <v>2730</v>
       </c>
       <c r="E15" t="n">
-        <v>241</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2730</v>
+        <v>1640</v>
       </c>
       <c r="E16" t="n">
-        <v>328</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1640</v>
+        <v>2124</v>
       </c>
       <c r="E17" t="n">
-        <v>197</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/05/03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2124</v>
+        <v>6560</v>
       </c>
       <c r="E18" t="n">
-        <v>255</v>
+        <v>787</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026/05/03</t>
+          <t>2026/05/23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6560</v>
+        <v>2124</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026/05/23</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2124</v>
+        <v>1539</v>
       </c>
       <c r="E20" t="n">
-        <v>255</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1539</v>
+        <v>6560</v>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>787</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>6560</v>
+        <v>5460</v>
       </c>
       <c r="E22" t="n">
-        <v>787</v>
+        <v>655</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>5460</v>
+        <v>3078</v>
       </c>
       <c r="E23" t="n">
-        <v>655</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3078</v>
+        <v>4248</v>
       </c>
       <c r="E24" t="n">
-        <v>369</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1611,38 +1611,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4248</v>
+        <v>2011</v>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026/05/27</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2011</v>
+        <v>5438</v>
       </c>
       <c r="E27" t="n">
-        <v>241</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28">
@@ -1653,122 +1653,122 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>5438</v>
+        <v>2011</v>
       </c>
       <c r="E28" t="n">
-        <v>653</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>2011</v>
+        <v>5460</v>
       </c>
       <c r="E29" t="n">
-        <v>241</v>
+        <v>655</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>5460</v>
+        <v>5438</v>
       </c>
       <c r="E30" t="n">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>5438</v>
+        <v>10920</v>
       </c>
       <c r="E31" t="n">
-        <v>653</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>10920</v>
+        <v>1640</v>
       </c>
       <c r="E32" t="n">
-        <v>1310</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026/05/17</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1640</v>
+        <v>10876</v>
       </c>
       <c r="E33" t="n">
-        <v>197</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -1832,112 +1832,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>10876</v>
+        <v>1539</v>
       </c>
       <c r="E4" t="n">
-        <v>1305</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1539</v>
+        <v>2124</v>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2124</v>
+        <v>4022</v>
       </c>
       <c r="E6" t="n">
-        <v>255</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4022</v>
+        <v>1640</v>
       </c>
       <c r="E7" t="n">
-        <v>483</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1640</v>
+        <v>5438</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1946,139 +1946,139 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5438</v>
+        <v>2719</v>
       </c>
       <c r="E9" t="n">
-        <v>653</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026/06/04</t>
+          <t>2026/06/14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2719</v>
+        <v>6560</v>
       </c>
       <c r="E10" t="n">
-        <v>326</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/06/14</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6560</v>
+        <v>1730</v>
       </c>
       <c r="E11" t="n">
-        <v>787</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1730</v>
+        <v>2719</v>
       </c>
       <c r="E12" t="n">
-        <v>208</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2719</v>
+        <v>3078</v>
       </c>
       <c r="E13" t="n">
-        <v>326</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/06/11</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3078</v>
+        <v>17708</v>
       </c>
       <c r="E14" t="n">
-        <v>369</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>17708</v>
+        <v>1539</v>
       </c>
       <c r="E15" t="n">
-        <v>2125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -2089,128 +2089,128 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1539</v>
+        <v>8496</v>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>8496</v>
+        <v>8044</v>
       </c>
       <c r="E17" t="n">
-        <v>1020</v>
+        <v>965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>8044</v>
+        <v>6920</v>
       </c>
       <c r="E18" t="n">
-        <v>965</v>
+        <v>830</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>6920</v>
+        <v>6156</v>
       </c>
       <c r="E19" t="n">
-        <v>830</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>6156</v>
+        <v>1640</v>
       </c>
       <c r="E20" t="n">
-        <v>739</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1640</v>
+        <v>5438</v>
       </c>
       <c r="E21" t="n">
-        <v>197</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2231,70 +2231,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5438</v>
+        <v>1730</v>
       </c>
       <c r="E23" t="n">
-        <v>653</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1730</v>
+        <v>2719</v>
       </c>
       <c r="E24" t="n">
-        <v>208</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2719</v>
+        <v>2124</v>
       </c>
       <c r="E25" t="n">
-        <v>326</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026/06/12</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2303,61 +2303,61 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>2124</v>
+        <v>4248</v>
       </c>
       <c r="E26" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>4248</v>
+        <v>10876</v>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_CO_150_JP</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>10876</v>
+        <v>6560</v>
       </c>
       <c r="E28" t="n">
-        <v>1305</v>
+        <v>787</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2366,103 +2366,103 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>6560</v>
+        <v>1640</v>
       </c>
       <c r="E29" t="n">
-        <v>787</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NR_CO_150_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1640</v>
+        <v>2011</v>
       </c>
       <c r="E30" t="n">
-        <v>197</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2011</v>
+        <v>2124</v>
       </c>
       <c r="E31" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>2124</v>
+        <v>4022</v>
       </c>
       <c r="E32" t="n">
-        <v>255</v>
+        <v>483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NR_CC_075_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>4022</v>
+        <v>8854</v>
       </c>
       <c r="E33" t="n">
-        <v>483</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026/06/14</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2471,82 +2471,82 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>8854</v>
+        <v>17708</v>
       </c>
       <c r="E34" t="n">
-        <v>1062</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>17708</v>
+        <v>5460</v>
       </c>
       <c r="E35" t="n">
-        <v>2125</v>
+        <v>655</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>5460</v>
+        <v>5438</v>
       </c>
       <c r="E36" t="n">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026/06/14</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>5438</v>
+        <v>5460</v>
       </c>
       <c r="E37" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026/06/12</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2567,196 +2567,196 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_SC_050_JP</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>5460</v>
+        <v>8496</v>
       </c>
       <c r="E39" t="n">
-        <v>655</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NR_SC_050_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>8496</v>
+        <v>3460</v>
       </c>
       <c r="E40" t="n">
-        <v>1020</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_PA_030_JP</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>3460</v>
+        <v>2730</v>
       </c>
       <c r="E41" t="n">
-        <v>415</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NR_PA_030_JP</t>
+          <t>NR_RE_020_JP</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>2730</v>
+        <v>5438</v>
       </c>
       <c r="E42" t="n">
-        <v>328</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NR_RE_020_JP</t>
+          <t>NR_EG_050_JP</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>5438</v>
+        <v>8854</v>
       </c>
       <c r="E43" t="n">
-        <v>653</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NR_EG_050_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>8854</v>
+        <v>3078</v>
       </c>
       <c r="E44" t="n">
-        <v>1062</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_VT_200_JP</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>3078</v>
+        <v>6920</v>
       </c>
       <c r="E45" t="n">
-        <v>369</v>
+        <v>830</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/06/11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NR_VT_200_JP</t>
+          <t>NR_CM_100_JP</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6920</v>
+        <v>1539</v>
       </c>
       <c r="E46" t="n">
-        <v>830</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026/06/11</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NR_CM_100_JP</t>
+          <t>NR_CC_075_JP</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1539</v>
+        <v>2011</v>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2789,16 +2789,16 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>6900</v>
+        <v>4700</v>
       </c>
       <c r="E49" t="n">
-        <v>828</v>
+        <v>564</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2810,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>6800</v>
+        <v>5000</v>
       </c>
       <c r="E50" t="n">
-        <v>816</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
